--- a/test-data/Test2.xlsx
+++ b/test-data/Test2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Home\Workspace\Mathi_WS\self\Phoenix\test-data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\supri\Pheonix\Phoenix\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2B8867-43E4-4736-B976-5D12D550B2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A68478-66ED-463C-8E2C-56C98EDF8BC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F7E53592-F92F-4807-91B6-69E42A286F67}"/>
+    <workbookView xWindow="6000" yWindow="3600" windowWidth="18000" windowHeight="9540" xr2:uid="{F7E53592-F92F-4807-91B6-69E42A286F67}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,14 +424,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CB928A-ACFE-487D-8D27-88888A74B9C7}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -442,7 +441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
